--- a/education_forms/025_faculty_satisfaction_survey--education_forms.xlsx
+++ b/education_forms/025_faculty_satisfaction_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,8 +819,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,12 +848,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'much_more_than_enough'}</t>
+          <t>much_more_than_enough</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Much more than enough'}</t>
+          <t>Much more than enough</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'just_enough'}</t>
+          <t>just_enough</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Just enough'}</t>
+          <t>Just enough</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'a_little_less_than_enough'}</t>
+          <t>a_little_less_than_enough</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'A little less than enough'}</t>
+          <t>A little less than enough</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
